--- a/Calendário 3ADM-TB.xlsx
+++ b/Calendário 3ADM-TB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desktop\Desktop\SENAI\02 - Disciplinas\05 - ADM\fim_semestre_2026_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desktop\Desktop\SENAI\02 - Disciplinas\fim_semestre_2026_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC1A475-DD77-4604-BB95-0FB2C64F08E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB11BEA-4BE6-43CF-BBC2-6A052FA391B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E39C29BC-6674-47EC-9BAE-59D878940E0F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t>MAIO</t>
   </si>
@@ -75,7 +75,10 @@
     <t>Aula de normal</t>
   </si>
   <si>
-    <t>Pode ter SAEP</t>
+    <t>Colocar no servidor o ChatBot</t>
+  </si>
+  <si>
+    <t>SAEP prático</t>
   </si>
 </sst>
 </file>
@@ -106,7 +109,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -158,6 +161,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3399"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -189,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -202,10 +211,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -214,6 +224,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF3399"/>
       <color rgb="FF00FF00"/>
       <color rgb="FFFF99FF"/>
     </mruColors>
@@ -526,31 +537,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93026AC0-F930-466F-A12C-11087F6972B3}">
-  <dimension ref="B2:S14"/>
+  <dimension ref="B2:S16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="45" width="3.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="J2" s="12" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="J2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
       <c r="R2" s="5"/>
       <c r="S2" s="6" t="s">
         <v>10</v>
@@ -629,7 +640,7 @@
         <v>23</v>
       </c>
       <c r="J4" s="4"/>
-      <c r="K4" s="2">
+      <c r="K4" s="14">
         <f>J4+1</f>
         <v>1</v>
       </c>
@@ -637,7 +648,7 @@
         <f t="shared" ref="L4:P4" si="1">K4+1</f>
         <v>2</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -679,7 +690,7 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
@@ -860,9 +871,15 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R14" s="13"/>
+      <c r="R14" s="12"/>
       <c r="S14" s="6" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="R16" s="14"/>
+      <c r="S16" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
